--- a/data/trans_bre/IP42B-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Provincia-trans_bre.xlsx
@@ -586,7 +586,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 22,39</t>
+          <t>-9,83; 21,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-47,52; 13,55</t>
+          <t>-46,39; 14,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 10,96</t>
+          <t>-20,83; 11,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,19 +654,19 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-82,54; 57,96</t>
+          <t>-84,82; 62,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 379,15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 33,01</t>
+          <t>-2,09; 31,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 14,17</t>
+          <t>-11,87; 13,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 17,11</t>
+          <t>-5,75; 16,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,19 +734,19 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,78; 167,67</t>
+          <t>-58,91; 188,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,93; 523,9</t>
+          <t>-58,72; 485,88</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,28</t>
+          <t>0,0; 30,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 7,67</t>
+          <t>-24,52; 7,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 17,03</t>
+          <t>-5,32; 14,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 34,52</t>
+          <t>-2,25; 36,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,74; 40,82</t>
+          <t>5,75; 42,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,18; 4,16</t>
+          <t>-22,29; 4,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,8</t>
+          <t>0,0; 77,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 46,63</t>
+          <t>-11,86; 51,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 13,9</t>
+          <t>-5,92; 17,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 26,36</t>
+          <t>3,11; 26,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 23,72</t>
+          <t>-16,57; 24,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,78; 5,03</t>
+          <t>-36,54; 6,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-24,0; -0,27</t>
+          <t>-23,93; 1,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 15,31</t>
+          <t>-16,72; 13,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 17,0</t>
+          <t>-2,78; 17,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 48,85</t>
+          <t>-100,0; 162,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-55,51; 124,34</t>
+          <t>-60,2; 119,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-67,61; 1421,78</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-29,23; 0,92</t>
+          <t>-30,05; 0,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 7,41</t>
+          <t>-7,91; 8,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 11,17</t>
+          <t>-6,38; 11,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 51,5</t>
+          <t>-100,0; 51,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 458,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,66; 505,6</t>
+          <t>-66,97; 559,61</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 6,95</t>
+          <t>-3,06; 7,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 8,27</t>
+          <t>-4,45; 7,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 4,9</t>
+          <t>-3,02; 5,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-34,47; 136,04</t>
+          <t>-33,99; 141,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-26,22; 78,12</t>
+          <t>-26,24; 65,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-34,48; 79,35</t>
+          <t>-34,51; 102,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP42B-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Provincia-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 21,46</t>
+          <t>-9,83; 22,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-46,39; 14,73</t>
+          <t>-48,81; 11,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 11,92</t>
+          <t>-23,07; 12,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-84,82; 62,99</t>
+          <t>-84,37; 48,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 379,15</t>
+          <t>-100,0; 351,53</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 31,04</t>
+          <t>0,91; 31,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 13,99</t>
+          <t>-13,32; 14,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 16,56</t>
+          <t>-6,14; 17,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,91; 188,64</t>
+          <t>-66,1; 165,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,72; 485,88</t>
+          <t>-55,46; 439,62</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,24</t>
+          <t>0,0; 30,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 7,42</t>
+          <t>-27,21; 7,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 14,42</t>
+          <t>-5,3; 16,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 36,33</t>
+          <t>-2,76; 34,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,75; 42,41</t>
+          <t>6,21; 40,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,29; 4,74</t>
+          <t>-20,47; 4,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,42</t>
+          <t>0,0; 79,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 51,52</t>
+          <t>-12,76; 51,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 17,25</t>
+          <t>-6,16; 17,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,11; 26,26</t>
+          <t>3,04; 24,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 24,11</t>
+          <t>-17,03; 22,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,54; 6,63</t>
+          <t>-34,89; 5,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1114,27 +1114,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-23,93; 1,6</t>
+          <t>-24,01; -0,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 13,92</t>
+          <t>-18,39; 13,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 17,4</t>
+          <t>-2,5; 16,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 162,96</t>
+          <t>-100,0; 77,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-60,2; 119,25</t>
+          <t>-61,06; 108,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,05; 0,0</t>
+          <t>-28,37; -0,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 8,02</t>
+          <t>-8,25; 8,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 11,75</t>
+          <t>-6,87; 11,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 51,93</t>
+          <t>-100,0; 45,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 489,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,97; 559,61</t>
+          <t>-70,43; 614,78</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 7,05</t>
+          <t>-3,26; 6,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 7,65</t>
+          <t>-4,14; 8,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 5,43</t>
+          <t>-2,95; 5,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-33,99; 141,77</t>
+          <t>-35,8; 141,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 65,4</t>
+          <t>-24,52; 75,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 102,89</t>
+          <t>-32,07; 107,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP42B-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Provincia-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 22,44</t>
+          <t>-9,77; 22,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-48,81; 11,91</t>
+          <t>-47,52; 13,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 12,24</t>
+          <t>-23,71; 10,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-84,37; 48,72</t>
+          <t>-82,54; 57,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 351,53</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 31,11</t>
+          <t>-0,24; 33,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 14,3</t>
+          <t>-13,23; 14,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 17,27</t>
+          <t>-5,04; 17,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,1; 165,21</t>
+          <t>-62,78; 167,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,46; 439,62</t>
+          <t>-52,93; 523,9</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,52</t>
+          <t>0,0; 28,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-27,21; 7,96</t>
+          <t>-24,1; 7,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 16,75</t>
+          <t>-5,29; 17,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 34,96</t>
+          <t>-1,37; 34,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 40,59</t>
+          <t>5,74; 40,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 4,31</t>
+          <t>-22,18; 4,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,5</t>
+          <t>0,0; 77,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 51,66</t>
+          <t>-11,53; 46,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 17,85</t>
+          <t>-6,12; 13,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,04; 24,5</t>
+          <t>3,08; 26,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 22,57</t>
+          <t>-14,97; 23,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,89; 5,06</t>
+          <t>-36,78; 5,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-24,01; -0,05</t>
+          <t>-24,0; -0,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 13,82</t>
+          <t>-16,34; 15,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 16,12</t>
+          <t>-2,63; 17,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 77,74</t>
+          <t>-100,0; 48,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-61,06; 108,98</t>
+          <t>-55,51; 124,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-67,61; 1421,78</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,37; -0,01</t>
+          <t>-29,23; 0,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 8,02</t>
+          <t>-8,94; 7,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 11,39</t>
+          <t>-6,57; 11,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 45,83</t>
+          <t>-100,0; 51,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 489,63</t>
+          <t>-100,0; 458,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,43; 614,78</t>
+          <t>-68,66; 505,6</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 6,83</t>
+          <t>-3,07; 6,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 8,18</t>
+          <t>-4,12; 8,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 5,68</t>
+          <t>-3,38; 4,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-35,8; 141,98</t>
+          <t>-34,47; 136,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 75,67</t>
+          <t>-26,22; 78,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 107,39</t>
+          <t>-34,48; 79,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP42B-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Provincia-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,151 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,13</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-17,09</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>43,49%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-40,8%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-30,17%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.130453261707947</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-17.09433315179986</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-4.303726775439519</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.4349422063697563</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.4080082195676779</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.3016632822781561</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-9,77; 22,39</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-47,52; 13,55</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-23,71; 10,96</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-82,54; 57,96</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-9.77233460028982</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-47.51820386125718</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-23.70692604394959</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n">
+        <v>-0.8253772189065887</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>22.38589293005321</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>13.54889324777725</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.96455743683791</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n">
+        <v>0.5795879150427682</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Cádiz</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>12,6</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,14</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>418,41%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>63,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,24; 33,01</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-13,23; 14,17</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,04; 17,11</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-62,78; 167,67</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-52,93; 523,9</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>12.59770011529106</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.7476945390160444</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5.137228014845112</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>4.184103197517555</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.05049591147894193</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.6327104462369356</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>8,88</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-5,48</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,55</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-57,43%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>58,88%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.2431739887143435</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-13.23117142418522</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.038379433954483</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n">
+        <v>-0.6278048741018752</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5292956989018948</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 28,28</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-24,1; 7,67</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,29; 17,03</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>33.00926531297142</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>14.16648151943512</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>17.11491153863525</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
+        <v>1.676674407994461</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>5.238971234555179</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +755,141 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>12,62</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>21,66</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-7,69</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>345,42%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>649,08%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-57,96%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>8.877420824148793</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-5.475761644836964</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.545750733407226</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.5743028841277659</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.5887628026933562</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,37; 34,52</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5,74; 40,82</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-22,18; 4,16</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-24.10484888532016</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.285461683486427</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Huelva</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>28.27606171707678</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.671628637598715</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>17.02949359805473</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>18,68</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>20,94</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,38</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>215,5%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>45,77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 77,8</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-11,53; 46,63</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-6,12; 13,9</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>12.61882526521742</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>21.66021296452433</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-7.691410431288393</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>3.454169456118206</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>6.490832797142943</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.579563412447745</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Jaén</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>9,77</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-8,95</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,71%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-64,39%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.373283790636211</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>5.736946431772198</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-22.18243947291315</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>3,08; 26,36</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-14,97; 23,72</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-36,78; 5,03</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>34.52240380984788</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>40.82299488013283</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.163916382536469</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,237 +897,387 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-9,87</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-1,62</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5,84</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-69,32%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-7,33%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>136,48%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>18.6821234259062</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>20.94157545891688</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.376728187755505</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>2.155037004203705</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.4576818238578971</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-24,0; -0,27</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-16,34; 15,31</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-2,63; 17,0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 48,85</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-55,51; 124,34</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-67,61; 1421,78</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-11.53151509920511</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-6.116646022166838</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+      <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>77.79512294815646</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>46.63300095105603</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>13.89503580746899</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-14,26</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-0,91</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2,14</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-70,57%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-14,43%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>33,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-29,23; 0,92</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-8,94; 7,41</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-6,57; 11,17</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 51,5</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 458,96</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-68,66; 505,6</t>
-        </is>
+      <c r="C19" s="5" t="n">
+        <v>9.765538815012841</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1.224223099701383</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-8.95340963000071</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.1170747080667978</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.643914257128297</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>25,55%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>3.084946357594077</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-14.96589873445451</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-36.78254253878171</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>-3,07; 6,95</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-4,12; 8,27</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-3,38; 4,9</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>-34,47; 136,04</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>-26,22; 78,12</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-34,48; 79,35</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>26.36025466714817</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>23.71858697087998</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>5.032513223021852</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-9.870650080226426</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-1.619716084538306</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>5.837680999958215</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>-0.6932295210619858</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.07329541868179767</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1.364811126079293</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-24.00050072306805</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-16.33676905118742</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-2.633224597884429</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.555147581908317</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.6761436362911465</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-0.2663931874894512</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>15.3108762144128</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>17.00379772562977</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0.4884863196677987</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>1.243445782639929</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>14.21776141522956</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>-14.26319624230571</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>-0.9104964378754452</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>2.138764227481209</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.7057219381688477</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.1443094843729442</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.3310242924232343</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-29.22924085968457</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>-8.938965370022093</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>-6.566762155174994</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.6865516511069703</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0.9173808135292706</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>7.411696317841485</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>11.16871327551579</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.5150208807469526</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>4.589645959517729</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>5.05598903613832</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>1.869401378026056</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1.756605808189621</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.9371912646043784</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>0.2555066936809234</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>0.1251437078747213</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>0.1251257214923607</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>-3.066655213804931</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-4.115552503575893</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-3.381218104972041</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>-0.3447460209054771</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>-0.2622286282783215</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>-0.3447813496249396</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>6.949389186567315</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>8.269951233547307</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>4.899031766782712</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>1.360435599647229</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0.7811743054328715</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>0.7934584600859568</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1313,17 +1286,17 @@
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
